--- a/content/Question Bank/MCQ/Unit 13 - Debugging/Unit 13 - Debugging - MCQ.xlsx
+++ b/content/Question Bank/MCQ/Unit 13 - Debugging/Unit 13 - Debugging - MCQ.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Python - MCQ - 13.1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Python - MCQ - 13.2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Python - MCQ - 13.3" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Python - MCQ - 13.4" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - MCQ - 13.1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - MCQ - 13.2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - MCQ - 13.3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - MCQ - 13.4" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -643,26 +643,26 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>try/except is technically illegal to use around intermittent errors at all</t>
+          <t>Silently ignoring exceptions always improves performance</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Silently ignoring exceptions always improves performance</t>
+          <t>It technically does not matter at all, since the error message is gone</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
+          <t>try/except is technically illegal to use around intermittent errors at all in Python</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
           <t>An unexplained, hidden bug usually reappears later, since its root cause was never addressed</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>It technically does not matter at all, since the error message is gone</t>
-        </is>
-      </c>
       <c r="Q2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -731,26 +731,26 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>The bug exists before either function runs, in how the list was originally built</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>The bug is inside load_counts, specifically in the return statement</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
           <t>There is no bug, since both prints ran successfully</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>The bug is inside load_counts, specifically in the return statement</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>The bug is inside total_rsvps, specifically in the `sum()` call</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>The bug exists before either function runs, in how the list was originally built</t>
-        </is>
-      </c>
       <c r="Q3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -813,26 +813,26 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>assert technically always passes no matter what the actual input value happens to be given here</t>
+          <t>assert technically always passes no matter what the actual input value happens to be given here, ever, no exceptions</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
+          <t>assert statements are technically removed automatically in every single Python version</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>assert technically cannot ever be used to check string methods like `isdigit()` at all, ever</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
           <t>assert is meant for catching impossible logic bugs, not validating expected user input, which should use if/raise or try/except</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>assert statements are technically removed automatically in every single Python version</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>assert technically cannot ever be used to check string methods like `isdigit()` at all, ever</t>
-        </is>
-      </c>
       <c r="Q4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -891,26 +891,26 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
+          <t>Python immediately raises an `AssertionError` at that line</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Nothing happens, regardless of the condition's truth value</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>The program pauses and waits for user input</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
           <t>Python prints a warning but continues running normally</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>The program pauses and waits for user input</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Python immediately raises an `AssertionError` at that line</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Nothing happens, regardless of the condition's truth value</t>
-        </is>
-      </c>
       <c r="Q5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -969,26 +969,26 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
+          <t>`debug()` function</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>`stop()` function</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>`breakpoint()`</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
           <t>`pause()` function</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>`debug()` function</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>`stop()` function</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>`breakpoint()`</t>
-        </is>
-      </c>
       <c r="Q6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -1057,26 +1057,26 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
+          <t>`None`, since pdb cannot report numeric variables</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2, since the addition line executed before pausing again</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
           <t>0, unchanged since nothing happened</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>An error, because total was never defined</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>`None`, since pdb cannot report numeric variables</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2, since the addition line executed before pausing again</t>
-        </is>
-      </c>
       <c r="Q7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -1135,26 +1135,26 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
+          <t>ERROR, CRITICAL, WARNING, INFO, DEBUG</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
           <t>DEBUG, INFO, WARNING, ERROR, CRITICAL</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>INFO, DEBUG, ERROR, WARNING, CRITICAL</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>CRITICAL, ERROR, WARNING, INFO, DEBUG</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>INFO, DEBUG, ERROR, WARNING, CRITICAL</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>ERROR, CRITICAL, WARNING, INFO, DEBUG</t>
-        </is>
-      </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -1218,21 +1218,21 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>The only technical fix is to replace all logging calls with `print()` statements entirely</t>
+          <t>Logging technically cannot ever be filtered once a program is already running</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Logging technically cannot ever be filtered once a program is already running</t>
+          <t>Changing the single basicConfig level setting silences detail messages without touching the original calls</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Changing the single basicConfig level setting silences detail messages without touching the original calls</t>
+          <t>The only technical fix is to replace all logging calls with `print()` statements entirely, everywhere</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -1291,26 +1291,26 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Add technically more print statements to every single file in the project</t>
+          <t>Delete the entire project completely and start over from scratch</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
+          <t>Reproduce the bug outside the full program, using only the specific data and code involved</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
           <t>Immediately ask an AI assistant without trying anything first</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>Reproduce the bug outside the full program, using only the specific data and code involved</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Delete the entire project completely and start over from scratch</t>
+          <t>Add technically many more print statements to every single file in the whole project</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1369,26 +1369,26 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Paste it in immediately since AI suggestions are technically always assumed correct</t>
+          <t>Read and understand the fix, then rerun the minimal failing case to verify the original error is actually gone</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
+          <t>Ask a second AI assistant to verify the first one's answer instead of testing it yourself</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Paste it in immediately since AI suggestions are technically always assumed to be entirely correct here</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
           <t>Reject all AI suggestions automatically without ever reading them at all</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>Read and understand the fix, then rerun the minimal failing case to verify the original error is actually gone</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Ask a second AI assistant to verify the first one's answer instead of testing it yourself</t>
-        </is>
-      </c>
       <c r="Q11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1548,26 +1548,26 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>It technically means the entire Python interpreter itself is broken</t>
+          <t>It technically means the entire Python interpreter itself is somehow broken permanently</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
+          <t>It is normal, useful information pointing at a specific gap between expectation and reality</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>It technically means you are simply not cut out for programming</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
           <t>It should be ignored and the program rerun until it works</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>It is normal, useful information pointing at a specific gap between expectation and reality</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>It technically means you are simply not cut out for programming</t>
-        </is>
-      </c>
       <c r="Q2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -1626,26 +1626,26 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>A learnable procedure of comparing expected behavior to actual behavior and narrowing the gap</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
           <t>A fixed personality trait that some people are technically born with</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>A process that technically only senior developers are able to perform</t>
-        </is>
-      </c>
       <c r="O3" t="inlineStr">
         <is>
+          <t>A process that technically only senior developers are ever able to perform well</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
           <t>Something that can only be done by rereading code silently</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>A learnable procedure of comparing expected behavior to actual behavior and narrowing the gap</t>
-        </is>
-      </c>
       <c r="Q3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -1704,26 +1704,26 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
+          <t>Placing deliberate temporary `print()` calls to observe values at each step of execution</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Printing only the final output of a program at the very end</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
           <t>A built-in Python function that technically finds bugs completely automatically</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Printing only the final output of a program at the very end</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>Printing the entire source code of a program out to a separate file</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Placing deliberate temporary `print()` calls to observe values at each step of execution</t>
-        </is>
-      </c>
       <c r="Q4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -1787,21 +1787,21 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
+          <t>Print debugging does not scale well here; an interactive debugger like pdb would be more effective</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>This is exactly when print debugging scales best, since it shows everything at once here</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
           <t>Print debugging is always the best tool regardless of bug depth</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>This is exactly when print debugging scales best, since it shows everything at once</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Print debugging does not scale well here; an interactive debugger like pdb would be more effective</t>
-        </is>
-      </c>
       <c r="Q5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -1860,12 +1860,12 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
+          <t>It is technically actually considered the fastest way to fix any bug</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
           <t>Python will technically refuse to run after three separate failed attempts</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>It is technically actually considered the fastest way to fix any bug</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1942,26 +1942,26 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>It technically proves the function is already completely broken and unusable</t>
+          <t>It has no real value since Python catches all such errors automatically</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
+          <t>It technically proves the function is already completely broken and entirely unusable now</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>It shows the habit of proactively questioning assumptions instead of discovering failures by accident</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
           <t>It technically means the entire function should simply be deleted</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>It has no real value since Python catches all such errors automatically</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>It shows the habit of proactively questioning assumptions instead of discovering failures by accident</t>
-        </is>
-      </c>
       <c r="Q7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -2025,14 +2025,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
+          <t>!r technically converts the value into an integer before it is ever printed</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
           <t>!r shows the precise `repr()` form, revealing hidden differences like trailing spaces or types that plain display hides</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>!r is technically required syntax and has absolutely no effect on the displayed text</t>
-        </is>
-      </c>
       <c r="O8" t="inlineStr">
         <is>
           <t>!r technically makes the entire program run measurably and noticeably faster</t>
@@ -2040,11 +2040,11 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>!r technically converts the value into an integer before it is ever printed</t>
+          <t>!r is technically required syntax and has absolutely no real effect on the displayed text at all here, ever, period</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -2108,21 +2108,21 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
+          <t>Leaving them in always causes a `SyntaxError`</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>They clutter real output and confuse future readers of the code</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
           <t>Python automatically deletes unused print statements</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>Leaving them in always causes a `SyntaxError`</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>They clutter real output and confuse future readers of the code</t>
-        </is>
-      </c>
       <c r="Q9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -2181,26 +2181,26 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
+          <t>assert can be disabled with -O, so checks that must always run need if/raise instead</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
           <t>if/raise is slower and only used for style reasons</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>assert cannot compare numbers, only strings</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
         <is>
           <t>There is no real difference; either could be replaced with the other freely</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>assert can be disabled with -O, so checks that must always run need if/raise instead</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>assert cannot compare numbers, only strings</t>
-        </is>
-      </c>
       <c r="Q10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>`breakpoint()` technically and automatically detects negative numbers without any placement needed</t>
+          <t>`breakpoint()` technically and automatically detects negative numbers without any placement being needed at all</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -2445,26 +2445,26 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>It raises `AssertionError`: attendees list must not be empty immediately at the assert line</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>It technically runs successfully every time and simply returns the value `None`</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>It raises `ZeroDivisionError` on the total / `len(attendees)` line</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
           <t>It technically returns the value 0 silently with no error at all</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>It technically runs successfully and simply returns the value `None`</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>It raises `ZeroDivisionError` on the total / `len(attendees)` line</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>It raises `AssertionError`: attendees list must not be empty immediately at the assert line</t>
-        </is>
-      </c>
       <c r="Q2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -2530,26 +2530,26 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>It allows max_attendees to be any negative number safely</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>It technically replaces the entire need for a constructor altogether</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>It technically makes the entire class run measurably faster</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
           <t>It documents the assumption directly in the code for any future reader</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>It allows max_attendees to be any negative number safely</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>It technically makes the entire class run measurably faster</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>It technically replaces the entire need for a constructor altogether</t>
-        </is>
-      </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -2617,17 +2617,17 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
+          <t>It technically pauses the entire program permanently, forever</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
           <t>It technically and permanently modifies the variable's value directly</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>It technically plots an entire graph of the variable's history</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>It technically pauses the entire program permanently, forever</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -2701,21 +2701,21 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>n and s technically behave in exactly an identical way in this situation</t>
+          <t>n runs over the whole call without pausing inside it, while s steps into the function itself</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
+          <t>n and s technically behave in exactly an identical way in this exact situation here</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
           <t>n steps into the function, while s skips over it entirely</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>n runs over the whole call without pausing inside it, while s steps into the function itself</t>
-        </is>
-      </c>
       <c r="Q5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -2774,22 +2774,22 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
+          <t>n technically prints all variables, while c prints only the current one</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>n runs the current line and pauses on the next, c resumes until the next breakpoint or the program ends</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>n technically quits the debugger entirely, while c only ever steps forward one single line at a time</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
           <t>n and c technically do exactly the same identical thing every time</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>n runs the current line and pauses on the next, c resumes until the next breakpoint or the program ends</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>n technically prints all variables, while c prints only the current one</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>n technically quits the debugger entirely, while c steps forward one line</t>
         </is>
       </c>
       <c r="Q6" t="n">
@@ -2852,22 +2852,22 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
+          <t>w</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>l</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
           <t>s</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>l</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>w</t>
         </is>
       </c>
       <c r="Q7" t="n">
@@ -2930,17 +2930,17 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
+          <t>The bug is narrowed to inside the inner function itself, since the value was correct beforehand</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
           <t>The bug must technically be in the caller instead, not the inner function</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>The bug technically cannot be determined at all from this information given</t>
-        </is>
-      </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>The bug is narrowed to inside the inner function itself, since the value was correct beforehand</t>
+          <t>The bug technically cannot be determined at all from this specific information given here</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -2949,7 +2949,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -3017,26 +3017,26 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
+          <t>The order in which functions will technically execute in the future</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>The order in which variables were technically created over time</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>A list of all functions defined anywhere in the file</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
           <t>The full call stack from the current paused line up to the outermost caller</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>The order in which functions will technically execute in the future</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>The order in which variables were technically created over time</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>A list of all functions defined anywhere in the file</t>
-        </is>
-      </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -3095,22 +3095,22 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
+          <t>p and pp</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>n and c</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>u and d</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
           <t>s and w</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>n and c</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>u and d</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>p and pp</t>
         </is>
       </c>
       <c r="Q10" t="n">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>It technically and automatically fixes any bug found anywhere in the entire call chain by itself</t>
+          <t>It technically and automatically fixes any bug found anywhere in the entire call chain by itself, instantly and silently</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -3365,17 +3365,17 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
+          <t>All four messages are shown</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Only the debug and info messages are shown</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
           <t>No messages are shown at all</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>All four messages are shown</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>Only the debug and info messages are shown</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -3438,26 +3438,26 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>`logging.error()`</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>`logging.debug()`</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
           <t>`logging.info()`</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>`logging.debug()`</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>`logging.error()`</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>`logging.warning()`</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -3516,26 +3516,26 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>`print()` and logging technically produce exactly identical output in absolutely every single case</t>
+          <t>`print()` and logging technically produce exactly identical output in absolutely every single case, always</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
+          <t>logging is technically only ever available in Python versions released after 3.10</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
           <t>logging labels severity, can be filtered by level, and can redirect to a file, all without editing the original calls</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>`print()` technically cannot ever accept f-strings while logging technically always can</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>logging is technically only ever available in Python versions released after 3.10</t>
-        </is>
-      </c>
       <c r="Q4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -3594,26 +3594,26 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
+          <t>To technically make the bug much harder to find on purpose here</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>To technically hide the bug entirely from other developers who are reviewing the code</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>To strip away unrelated code until the smallest reproduction that still triggers the bug remains</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
           <t>To technically rewrite the entire program completely from scratch every time</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>To technically hide the bug entirely from other developers reviewing the code</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>To technically make the bug much harder to find on purpose here</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>To strip away unrelated code until the smallest reproduction that still triggers the bug remains</t>
-        </is>
-      </c>
       <c r="Q5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -3672,26 +3672,26 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
+          <t>It technically only works because rubber ducks are considered good listeners</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Speaking forces explicit statement of assumptions that silent skimming lets slide past</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>It works by literally compiling the spoken words into code</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
           <t>The duck technically provides hints based on machine learning models</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>It technically only works because ducks are considered good listeners</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>It works by literally compiling the spoken words into code</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Speaking forces explicit statement of assumptions that silent skimming lets slide past</t>
-        </is>
-      </c>
       <c r="Q6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -3750,26 +3750,26 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
+          <t>Yes, technically any reproduction that crashes is automatically considered fully minimal already</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
           <t>Yes, because removing more code would change the error message</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Yes, technically any reproduction that crashes is automatically considered minimal</t>
-        </is>
-      </c>
       <c r="O7" t="inlineStr">
         <is>
+          <t>No, minimization should restart from the entire original project</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
           <t>No, since the class was shown unnecessary it should be dropped and stripping should continue further</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>No, minimization should restart from the entire original project</t>
-        </is>
-      </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -3837,17 +3837,17 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>The bug technically only ever happens when classes are being used</t>
+          <t>`sum()` technically cannot ever be used on any list containing numbers</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>`sum()` technically cannot ever be used on any list containing numbers</t>
+          <t>The Attendee class is definitely the cause of the bug</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>The Attendee class is definitely the cause of the bug</t>
+          <t>The bug technically only ever happens whenever classes are actually being used</t>
         </is>
       </c>
       <c r="Q8" t="n">
@@ -3910,26 +3910,26 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
+          <t>It automatically fixes the bug without needing other tools</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Fewer moving parts make applying any other debugging tool faster and clearer</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>It technically only ever helps if the bug happens to be a syntax error</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
           <t>It technically does not actually help any other tool at all</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>It technically only ever helps if the bug happens to be a syntax error</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>Fewer moving parts make applying any other debugging tool faster and clearer</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>It automatically fixes the bug without needing other tools</t>
-        </is>
-      </c>
       <c r="Q9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -3988,26 +3988,26 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
+          <t>What is my salary, what is the deadline, who do I ask, and what exactly is the bug ticket number here</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
           <t>Is the code fast, is the code short, is the code tested, is the code documented</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>What language is this, who wrote it, when was it written, is it formatted well</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
         <is>
           <t>What did I expect, what does it actually do, what does the error say bottom-up, where would the bad value sneak in</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>What is my salary, what is the deadline, who do I ask, what is the bug ticket number</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>What language is this, who wrote it, when was it written, is it formatted well</t>
-        </is>
-      </c>
       <c r="Q10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Strong questions are technically thought to be against most community guidelines in general, supposedly</t>
+          <t>Strong questions are technically thought to be against most online community guidelines in general, supposedly, everywhere</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -4076,12 +4076,12 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
+          <t>There is technically no real difference at all between the two kinds of questions asked</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
           <t>Weak questions are actually technically answered much faster because they are shorter</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>There is technically no real difference at all between the two kinds of questions asked</t>
         </is>
       </c>
       <c r="Q11" t="n">

--- a/content/Question Bank/MCQ/Unit 13 - Debugging/Unit 13 - Debugging - MCQ.xlsx
+++ b/content/Question Bank/MCQ/Unit 13 - Debugging/Unit 13 - Debugging - MCQ.xlsx
@@ -688,7 +688,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Since the bad value appears unchanged at every printed step, the problem is not introduced inside load_counts or total_rsvps; it must already exist in whatever code built the original list before either function ran.</t>
+          <t>Since the bad value appears unchanged at every printed step, the problem is not introduced inside `load_counts` or `total_rsvps`; it must already exist in whatever code built the original list before either function ran.</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -736,7 +736,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>The bug is inside load_counts, specifically in the return statement</t>
+          <t>The bug is inside `load_counts`, specifically in the return statement</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>The bug is inside total_rsvps, specifically in the `sum()` call</t>
+          <t>The bug is inside `total_rsvps`, specifically in the `sum()` call</t>
         </is>
       </c>
       <c r="Q3" t="n">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Typing n ran the line total += `attendee.rsvp_count`, which added the current attendee's rsvp_count of 2 to the previous total of 0, so the second check correctly reports total as 2.</t>
+          <t>Typing n ran the line total += `attendee.rsvp_count`, which added the current attendee's `rsvp_count` of 2 to the previous total of 0, so the second check correctly reports total as 2.</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Anticipating which inputs would break a function, here a team_size of 0 causing a `ZeroDivisionError`, shows the habit of asking 'what input would break this' proactively, which is exactly the calm, structured questioning this mindset is meant to build.</t>
+          <t>Anticipating which inputs would break a function, here a `team_size` of 0 causing a `ZeroDivisionError`, shows the habit of asking 'what input would break this' proactively, which is exactly the calm, structured questioning this mindset is meant to build.</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -2211,12 +2211,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A developer suspects a bug occurs only when a specific attendee's rsvp_count is negative, inside a loop processing many attendees. What is the most effective use of `breakpoint()` here?</t>
+          <t>A developer suspects a bug occurs only when a specific attendee's `rsvp_count` is negative, inside a loop processing many attendees. What is the most effective use of `breakpoint()` here?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Placing `breakpoint()` inside the loop body lets the developer pause on every iteration and inspect each attendee's rsvp_count directly, or combine it with a conditional check so the pause only triggers when the suspicious condition is actually met, rather than guessing from outside the loop.</t>
+          <t>Placing `breakpoint()` inside the loop body lets the developer pause on every iteration and inspect each attendee's `rsvp_count` directly, or combine it with a conditional check so the pause only triggers when the suspicious condition is actually met, rather than guessing from outside the loop.</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>It allows max_attendees to be any negative number safely</t>
+          <t>It allows `max_attendees` to be any negative number safely</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -2653,7 +2653,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>n runs the entire total_rsvps call as one step and pauses on the line after it without ever showing what happened inside, while s steps into total_rsvps itself, pausing at its very first line so you can follow execution downward into that function.</t>
+          <t>n runs the entire `total_rsvps` call as one step and pauses on the line after it without ever showing what happened inside, while s steps into `total_rsvps` itself, pausing at its very first line so you can follow execution downward into that function.</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -3047,12 +3047,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Paused deep inside total_rsvps, a developer wants to check the value of attendees back in summarize_event without resuming execution. Which commands accomplish this?</t>
+          <t>Paused deep inside `total_rsvps`, a developer wants to check the value of attendees back in `summarize_event` without resuming execution. Which commands accomplish this?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>u (up) moves the inspection point one level up the call stack to the caller, summarize_event, allowing inspection of its local variables like attendees without resuming, and d (down) moves back down toward the current paused line afterward.</t>
+          <t>u (up) moves the inspection point one level up the call stack to the caller, `summarize_event`, allowing inspection of its local variables like attendees without resuming, and d (down) moves back down toward the current paused line afterward.</t>
         </is>
       </c>
       <c r="D10" t="n">

--- a/content/Question Bank/MCQ/Unit 13 - Debugging/Unit 13 - Debugging - MCQ.xlsx
+++ b/content/Question Bank/MCQ/Unit 13 - Debugging/Unit 13 - Debugging - MCQ.xlsx
@@ -2133,7 +2133,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A developer finishes tracking down a stubborn bug in a quiz app by scattering several temporary print statements through the scoring function, and the bug is now fixed. Why should debug `print()` statements added temporarily during investigation be removed or commented out once the bug is fixed?</t>
+          <t>A developer uses assert to check that a bank withdrawal never overdraws the account, planning to rely on that check even in production. Why is assert risky for a check that must always run, and what should be used instead?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
